--- a/zestawienie przyklad 1.xlsx
+++ b/zestawienie przyklad 1.xlsx
@@ -3,15 +3,15 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
     <sheet name="zestawienie" sheetId="1" r:id="rId1"/>
-    <sheet name="05-0497" sheetId="2" r:id="rId2"/>
-    <sheet name="05-0498" sheetId="3" r:id="rId3"/>
-    <sheet name="05-0504" sheetId="4" r:id="rId4"/>
-    <sheet name="05-0505" sheetId="5" r:id="rId5"/>
-    <sheet name="05-0506" sheetId="6" r:id="rId6"/>
-    <sheet name="05-0507" sheetId="7" r:id="rId7"/>
-    <sheet name="05-0982" sheetId="8" r:id="rId8"/>
-    <sheet name="obszar_4" sheetId="9" r:id="rId9"/>
-    <sheet name="uwagi" sheetId="10" r:id="rId10"/>
+    <sheet name="kontrola" sheetId="2" r:id="rId2"/>
+    <sheet name="05-0497" sheetId="3" r:id="rId3"/>
+    <sheet name="05-0498" sheetId="4" r:id="rId4"/>
+    <sheet name="05-0504" sheetId="5" r:id="rId5"/>
+    <sheet name="05-0505" sheetId="6" r:id="rId6"/>
+    <sheet name="05-0506" sheetId="7" r:id="rId7"/>
+    <sheet name="05-0507" sheetId="8" r:id="rId8"/>
+    <sheet name="05-0982" sheetId="9" r:id="rId9"/>
+    <sheet name="obszar_4" sheetId="10" r:id="rId10"/>
   </sheets>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>
@@ -30,12 +30,30 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2B3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8B4B4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -50,9 +68,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
 </styleSheet>
 </file>
@@ -63,6 +84,7 @@
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="24" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -81,20 +103,30 @@
           <t xml:space="preserve">długość</t>
         </is>
       </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kontrola</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">05-0497</t>
         </is>
       </c>
-      <c r="B2">
+      <c r="B2" s="3">
         <f>COUNTA('05-0497'!A:A)-1</f>
         <v>29</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="3">
         <f>SUM('05-0497'!D:D)</f>
         <v>1023</v>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 błędów, 2 uwag</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -111,6 +143,11 @@
         <f>SUM('05-0498'!D:D)</f>
         <v>692</v>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OK</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -126,50 +163,70 @@
         <f>SUM('05-0504'!D:D)</f>
         <v>526</v>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OK</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">05-0505</t>
         </is>
       </c>
-      <c r="B5">
+      <c r="B5" s="2">
         <f>COUNTA('05-0505'!A:A)-1</f>
         <v>13</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="2">
         <f>SUM('05-0505'!D:D)</f>
         <v>433</v>
       </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 uwag</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">05-0506</t>
         </is>
       </c>
-      <c r="B6">
+      <c r="B6" s="2">
         <f>COUNTA('05-0506'!A:A)-1</f>
         <v>28</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="2">
         <f>SUM('05-0506'!D:D)</f>
         <v>1042</v>
       </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4 uwag</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">05-0507</t>
         </is>
       </c>
-      <c r="B7">
+      <c r="B7" s="3">
         <f>COUNTA('05-0507'!A:A)-1</f>
         <v>55</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="3">
         <f>SUM('05-0507'!D:D)</f>
         <v>2162</v>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 błędów, 1 uwag</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -186,20 +243,30 @@
         <f>SUM('05-0982'!D:D)</f>
         <v>1615</v>
       </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OK</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">obszar_4</t>
         </is>
       </c>
-      <c r="B9">
+      <c r="B9" s="3">
         <f>COUNTA('obszar_4'!A:A)-1</f>
         <v>20</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="3">
         <f>SUM('obszar_4'!D:D)</f>
         <v>756</v>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4 błędów, 1 uwag</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -215,6 +282,11 @@
       <c r="C10">
         <f>SUM(C2:C9)</f>
         <v>8249</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patrz arkusz "kontrola"</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -222,107 +294,6 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <cols>
-    <col min="1" max="1" width="140" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Uwagi do sprawdzenia</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Zdublowany opis słupu "słup nN P-10/ZN" w punkcie (7532752.96, 5765369.38) - pominięto.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Zdublowany opis słupu "słup nN P-10/ZN" w punkcie (7531182.57, 5767465.73) - pominięto.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Zdublowany opis słupu "słup nN P-10/ZN" w punkcie (7531113.88, 5768370.52) - pominięto.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Numer "10.1" (7530080.86, 5768361.33) nie został przypisany do żadnego słupu.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Słup nr 1 (7533133.51, 5766624.45): brak opisu stacji w zakresie - nazwa "obszar_4" (do uzupełnienia).</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Słup nr 1 (7533091.58, 5766535.89): brak opisu stacji w zakresie - nazwa "obszar_4" (do uzupełnienia).</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Słup nr 2.1 (7530526.49, 5768275.45): brak wymiaru do słupa 2 - podzielono wymiar 52 m ze słupem 2.2.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Słup nr 1 (7533133.51, 5766624.45) stacji obszar_4: nie można ustalić odległości - uzupełnij ręcznie.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Słup nr 2 (7533196.90, 5766750.17): brak wymiaru do słupa 1 - podzielono wymiar 48 m ze słupem 3.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Stacja 05-0506: nie rozpoznano opisu obwodu dla słupa nr 1 (7531044.11, 5767589.13) - przyjęto obwód 2.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Stacja 05-0506: powtórzony numer obwodu w opisach "obw. nr" - sprawdź przypisanie obwodów.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Stacja obszar_4: powtórzony numer obwodu w opisach "obw. nr" - sprawdź przypisanie obwodów.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -331,6 +302,7 @@
     <col min="4" max="4" width="11" customWidth="1"/>
     <col min="5" max="5" width="8" customWidth="1"/>
     <col min="6" max="6" width="8" customWidth="1"/>
+    <col min="7" max="7" width="90" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -364,48 +336,59 @@
           <t xml:space="preserve">Obwód</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kontrola</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RPK</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-10.5/10/E</t>
-        </is>
-      </c>
-      <c r="D2">
-        <v>16</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-10/ZN</t>
+        </is>
+      </c>
+      <c r="D2" s="3">
+        <v>24</v>
+      </c>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3">
+        <v>1</v>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BŁĄD: Brak opisu "STACJA TRAFO" w zakresie - arkusz nazwano "obszar_4" (popraw nazwę).</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">K</t>
+          <t xml:space="preserve">P</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">-10.5/10/E</t>
+          <t xml:space="preserve">-10/ZN</t>
         </is>
       </c>
       <c r="D3">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -414,7 +397,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -428,7 +411,7 @@
         </is>
       </c>
       <c r="D4">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="F4">
         <v>1</v>
@@ -437,7 +420,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -451,7 +434,7 @@
         </is>
       </c>
       <c r="D5">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="F5">
         <v>1</v>
@@ -460,12 +443,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">P</t>
+          <t xml:space="preserve">RPKr</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -474,7 +457,7 @@
         </is>
       </c>
       <c r="D6">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -483,21 +466,21 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">RPK</t>
+          <t xml:space="preserve">P</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">-10.5/10/E</t>
+          <t xml:space="preserve">-10/ZN</t>
         </is>
       </c>
       <c r="D7">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="F7">
         <v>1</v>
@@ -506,12 +489,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">P</t>
+          <t xml:space="preserve">Nr</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -520,7 +503,7 @@
         </is>
       </c>
       <c r="D8">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="F8">
         <v>1</v>
@@ -529,21 +512,21 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.7</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">K</t>
+          <t xml:space="preserve">P</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">-10.5/10/E</t>
+          <t xml:space="preserve">-10/ZN</t>
         </is>
       </c>
       <c r="D9">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="F9">
         <v>1</v>
@@ -552,21 +535,21 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.8</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">P</t>
+          <t xml:space="preserve">N</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">-10/ZN</t>
+          <t xml:space="preserve">-10.5/10/E</t>
         </is>
       </c>
       <c r="D10">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F10">
         <v>1</v>
@@ -575,76 +558,86 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.9</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">N</t>
+          <t xml:space="preserve">P</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-10.5/10/E</t>
+          <t xml:space="preserve">-10/ZN</t>
         </is>
       </c>
       <c r="D11">
-        <v>54</v>
+        <v>18</v>
       </c>
       <c r="F11">
         <v>1</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1.10</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">K</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-10.5/10/E</t>
-        </is>
-      </c>
-      <c r="D12">
-        <v>56</v>
-      </c>
-      <c r="F12">
-        <v>1</v>
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Or</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-10/ZN</t>
+        </is>
+      </c>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3">
+        <v>2</v>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BŁĄD: Brak opisu "STACJA TRAFO" w zakresie - arkusz nazwano "obszar_4" (popraw nazwę). | BŁĄD: Nie można ustalić odległości - uzupełnij ręcznie.</t>
+        </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-10/ZN</t>
-        </is>
-      </c>
-      <c r="D13">
-        <v>31</v>
-      </c>
-      <c r="F13">
-        <v>1</v>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RPKr</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-10/ZN</t>
+        </is>
+      </c>
+      <c r="D13" s="3">
+        <v>24</v>
+      </c>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3">
+        <v>2</v>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BŁĄD: Brak wymiaru do słupa nr 1 - odległość ustalona przez podział wymiaru 48 m ze słupem nr 3 (dorysuj wymiar).</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2.1</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -658,21 +651,21 @@
         </is>
       </c>
       <c r="D14">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="F14">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2.2</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">P</t>
+          <t xml:space="preserve">Kr</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -681,16 +674,16 @@
         </is>
       </c>
       <c r="D15">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="F15">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -704,16 +697,16 @@
         </is>
       </c>
       <c r="D16">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="F16">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -727,16 +720,16 @@
         </is>
       </c>
       <c r="D17">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="F17">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -750,21 +743,21 @@
         </is>
       </c>
       <c r="D18">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="F18">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nr</t>
+          <t xml:space="preserve">P</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -773,21 +766,21 @@
         </is>
       </c>
       <c r="D19">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="F19">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nr</t>
+          <t xml:space="preserve">P</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -796,16 +789,16 @@
         </is>
       </c>
       <c r="D20">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="F20">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -819,217 +812,605 @@
         </is>
       </c>
       <c r="D21">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
+    <col min="1" max="1" width="9" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="8" customWidth="1"/>
+    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="5" max="5" width="110" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="7" max="7" width="13" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Poziom</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stacja</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Obwód</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nr słupa</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Opis</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BŁĄD</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05-0497</t>
+        </is>
+      </c>
+      <c r="C2" s="3">
+        <v>1</v>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Słup nr 1.2 leży bliżej stacji niż słup nr 1 - numery mogą być zamienione.</t>
+        </is>
+      </c>
+      <c r="F2" s="3">
+        <v>7532722.33</v>
+      </c>
+      <c r="G2" s="3">
+        <v>5765380.05</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BŁĄD</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05-0507</t>
+        </is>
+      </c>
+      <c r="C3" s="3">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.1</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Brak wymiaru do słupa nr 2 - odległość ustalona przez podział wymiaru 52 m ze słupem nr 2.2 (dorysuj wymiar).</t>
+        </is>
+      </c>
+      <c r="F3" s="3">
+        <v>7530526.49</v>
+      </c>
+      <c r="G3" s="3">
+        <v>5768275.45</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BŁĄD</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">obszar_4</t>
+        </is>
+      </c>
+      <c r="C4" s="3">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Brak opisu "STACJA TRAFO" w zakresie - arkusz nazwano "obszar_4" (popraw nazwę).</t>
+        </is>
+      </c>
+      <c r="F4" s="3">
+        <v>7533091.58</v>
+      </c>
+      <c r="G4" s="3">
+        <v>5766535.89</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BŁĄD</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">obszar_4</t>
+        </is>
+      </c>
+      <c r="C5" s="3">
+        <v>2</v>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Brak opisu "STACJA TRAFO" w zakresie - arkusz nazwano "obszar_4" (popraw nazwę).</t>
+        </is>
+      </c>
+      <c r="F5" s="3">
+        <v>7533133.51</v>
+      </c>
+      <c r="G5" s="3">
+        <v>5766624.45</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BŁĄD</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">obszar_4</t>
+        </is>
+      </c>
+      <c r="C6" s="3">
+        <v>2</v>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nie można ustalić odległości - uzupełnij ręcznie.</t>
+        </is>
+      </c>
+      <c r="F6" s="3">
+        <v>7533133.51</v>
+      </c>
+      <c r="G6" s="3">
+        <v>5766624.45</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BŁĄD</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">obszar_4</t>
+        </is>
+      </c>
+      <c r="C7" s="3">
+        <v>2</v>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Brak wymiaru do słupa nr 1 - odległość ustalona przez podział wymiaru 48 m ze słupem nr 3 (dorysuj wymiar).</t>
+        </is>
+      </c>
+      <c r="F7" s="3">
+        <v>7533196.9</v>
+      </c>
+      <c r="G7" s="3">
+        <v>5766750.17</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UWAGA</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05-0497</t>
+        </is>
+      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zdublowany opis słupu "słup nN P-10/ZN" - pominięto duplikat.</t>
+        </is>
+      </c>
+      <c r="F8" s="2">
+        <v>7532752.96</v>
+      </c>
+      <c r="G8" s="2">
+        <v>5765369.38</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UWAGA</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05-0497</t>
+        </is>
+      </c>
+      <c r="C9" s="2">
+        <v>2</v>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wymiar 54 m łączy słup nr 7 (stacja 05-0497) ze słupem nr 3 (stacja 05-0498) - przęsło między stacjami, nie wliczono go do zestawienia.</t>
+        </is>
+      </c>
+      <c r="F9" s="2">
+        <v>7532739.63</v>
+      </c>
+      <c r="G9" s="2">
+        <v>5765062.93</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UWAGA</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05-0505</t>
+        </is>
+      </c>
+      <c r="C10" s="2">
+        <v>2</v>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wymiar 31 m łączy słup nr 6 (stacja 05-0505) ze słupem nr 5 (stacja 05-0504) - przęsło między stacjami, nie wliczono go do zestawienia.</t>
+        </is>
+      </c>
+      <c r="F10" s="2">
+        <v>7532485.56</v>
+      </c>
+      <c r="G10" s="2">
+        <v>5765938.8</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UWAGA</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05-0506</t>
+        </is>
+      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zdublowany opis słupu "słup nN P-10/ZN" - pominięto duplikat.</t>
+        </is>
+      </c>
+      <c r="F11" s="2">
+        <v>7531182.57</v>
+      </c>
+      <c r="G11" s="2">
+        <v>5767465.73</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UWAGA</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05-0506</t>
+        </is>
+      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Powtórzony numer obwodu w opisach "obw. nr" - sprawdź numery obwodów.</t>
+        </is>
+      </c>
+      <c r="F12" s="2">
+        <v>7531037.23</v>
+      </c>
+      <c r="G12" s="2">
+        <v>5767592.37</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UWAGA</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05-0506</t>
+        </is>
+      </c>
+      <c r="C13" s="2">
+        <v>2</v>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nie rozpoznano opisu "obw. nr" dla tego obwodu - przyjęto obwód 2.</t>
+        </is>
+      </c>
+      <c r="F13" s="2">
+        <v>7531044.11</v>
+      </c>
+      <c r="G13" s="2">
+        <v>5767589.13</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UWAGA</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05-0506</t>
+        </is>
+      </c>
+      <c r="C14" s="2">
+        <v>2</v>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">11</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-10/ZN</t>
-        </is>
-      </c>
-      <c r="D22">
-        <v>35</v>
-      </c>
-      <c r="F22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Nr</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-10/ZN</t>
-        </is>
-      </c>
-      <c r="D23">
-        <v>41</v>
-      </c>
-      <c r="F23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-10/ZN</t>
-        </is>
-      </c>
-      <c r="D24">
-        <v>21</v>
-      </c>
-      <c r="F24">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-10/ZN</t>
-        </is>
-      </c>
-      <c r="D25">
-        <v>20</v>
-      </c>
-      <c r="F25">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wymiar 46 m łączy słup nr 11 (stacja 05-0506) ze słupem nr 10 (stacja 05-0982) - przęsło między stacjami, nie wliczono go do zestawienia.</t>
+        </is>
+      </c>
+      <c r="F14" s="2">
+        <v>7531361.4</v>
+      </c>
+      <c r="G14" s="2">
+        <v>5767309.33</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UWAGA</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05-0507</t>
+        </is>
+      </c>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zdublowany opis słupu "słup nN P-10/ZN" - pominięto duplikat.</t>
+        </is>
+      </c>
+      <c r="F15" s="2">
+        <v>7531113.88</v>
+      </c>
+      <c r="G15" s="2">
+        <v>5768370.52</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UWAGA</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">obszar_4</t>
+        </is>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Powtórzony numer obwodu w opisach "obw. nr" - sprawdź numery obwodów.</t>
+        </is>
+      </c>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INFO</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05-0498</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Numer "4" leży prawie tak samo blisko innego słupu (8.7 m wobec 8.4 m) - sprawdź, czy dotyczy właściwego słupu.</t>
+        </is>
+      </c>
+      <c r="F17">
+        <v>7532628.58</v>
+      </c>
+      <c r="G17">
+        <v>5764792.18</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INFO</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05-0498</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>2</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Numer "6" leży prawie tak samo blisko innego słupu (5.6 m wobec 3.5 m) - sprawdź, czy dotyczy właściwego słupu.</t>
+        </is>
+      </c>
+      <c r="F18">
+        <v>7532847.59</v>
+      </c>
+      <c r="G18">
+        <v>5765023.6</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INFO</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05-0507</t>
+        </is>
+      </c>
+      <c r="C19">
+        <v>2</v>
+      </c>
+      <c r="D19" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-10/ZN</t>
-        </is>
-      </c>
-      <c r="D26">
-        <v>43</v>
-      </c>
-      <c r="F26">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-10/ZN</t>
-        </is>
-      </c>
-      <c r="D27">
-        <v>38</v>
-      </c>
-      <c r="F27">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-10/ZN</t>
-        </is>
-      </c>
-      <c r="D28">
-        <v>43</v>
-      </c>
-      <c r="F28">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-10/ZN</t>
-        </is>
-      </c>
-      <c r="D29">
-        <v>43</v>
-      </c>
-      <c r="F29">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-10/ZN</t>
-        </is>
-      </c>
-      <c r="D30">
-        <v>46</v>
-      </c>
-      <c r="F30">
-        <v>2</v>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Numer "3" leży prawie tak samo blisko innego słupu (4.1 m wobec 3.9 m) - sprawdź, czy dotyczy właściwego słupu.</t>
+        </is>
+      </c>
+      <c r="F19">
+        <v>7530581.28</v>
+      </c>
+      <c r="G19">
+        <v>5768077.66</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INFO</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Numer "10.1" nie został przypisany do żadnego słupu.</t>
+        </is>
+      </c>
+      <c r="F20">
+        <v>7530080.86</v>
+      </c>
+      <c r="G20">
+        <v>5768361.33</v>
       </c>
     </row>
   </sheetData>
@@ -1045,6 +1426,7 @@
     <col min="4" max="4" width="11" customWidth="1"/>
     <col min="5" max="5" width="8" customWidth="1"/>
     <col min="6" max="6" width="8" customWidth="1"/>
+    <col min="7" max="7" width="90" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1078,48 +1460,59 @@
           <t xml:space="preserve">Obwód</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kontrola</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-10/ZN</t>
-        </is>
-      </c>
-      <c r="D2">
-        <v>9</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RPK</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-10.5/10/E</t>
+        </is>
+      </c>
+      <c r="D2" s="3">
+        <v>16</v>
+      </c>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3">
+        <v>1</v>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BŁĄD: Słup nr 1.2 leży bliżej stacji niż słup nr 1 - numery mogą być zamienione.</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1.1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">RPKr</t>
+          <t xml:space="preserve">K</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">-10/ZN</t>
+          <t xml:space="preserve">-10.5/10/E</t>
         </is>
       </c>
       <c r="D3">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -1128,7 +1521,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1.2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1142,7 +1535,7 @@
         </is>
       </c>
       <c r="D4">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="F4">
         <v>1</v>
@@ -1151,12 +1544,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1.3</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nr</t>
+          <t xml:space="preserve">P</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1165,7 +1558,7 @@
         </is>
       </c>
       <c r="D5">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F5">
         <v>1</v>
@@ -1174,12 +1567,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1.4</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nr</t>
+          <t xml:space="preserve">P</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1188,7 +1581,7 @@
         </is>
       </c>
       <c r="D6">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -1197,21 +1590,21 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1.5</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">P</t>
+          <t xml:space="preserve">RPK</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">-10/ZN</t>
+          <t xml:space="preserve">-10.5/10/E</t>
         </is>
       </c>
       <c r="D7">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="F7">
         <v>1</v>
@@ -1220,7 +1613,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1.6</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1234,7 +1627,7 @@
         </is>
       </c>
       <c r="D8">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="F8">
         <v>1</v>
@@ -1243,7 +1636,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1.7</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1257,7 +1650,7 @@
         </is>
       </c>
       <c r="D9">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="F9">
         <v>1</v>
@@ -1266,7 +1659,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">1.8</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1280,44 +1673,44 @@
         </is>
       </c>
       <c r="D10">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="F10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1.9</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">P</t>
+          <t xml:space="preserve">N</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-10/ZN</t>
+          <t xml:space="preserve">-10.5/10/E</t>
         </is>
       </c>
       <c r="D11">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="F11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1.10</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">RPK</t>
+          <t xml:space="preserve">K</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1326,90 +1719,90 @@
         </is>
       </c>
       <c r="D12">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="F12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">RPK</t>
+          <t xml:space="preserve">P</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">-10.5/10/E</t>
+          <t xml:space="preserve">-10/ZN</t>
         </is>
       </c>
       <c r="D13">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="F13">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">N</t>
+          <t xml:space="preserve">P</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">-10.5/10/E</t>
+          <t xml:space="preserve">-10/ZN</t>
         </is>
       </c>
       <c r="D14">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="F14">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">RPK</t>
+          <t xml:space="preserve">P</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">-10.5/10/E</t>
+          <t xml:space="preserve">-10/ZN</t>
         </is>
       </c>
       <c r="D15">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="F15">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">6.1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nr</t>
+          <t xml:space="preserve">P</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1418,21 +1811,21 @@
         </is>
       </c>
       <c r="D16">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="F16">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">6.2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kr</t>
+          <t xml:space="preserve">P</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1441,10 +1834,10 @@
         </is>
       </c>
       <c r="D17">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="F17">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1464,10 +1857,10 @@
         </is>
       </c>
       <c r="D18">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="F18">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1478,7 +1871,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">P</t>
+          <t xml:space="preserve">Nr</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1487,10 +1880,10 @@
         </is>
       </c>
       <c r="D19">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="F19">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1501,7 +1894,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">P</t>
+          <t xml:space="preserve">Nr</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1510,10 +1903,10 @@
         </is>
       </c>
       <c r="D20">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="F20">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1524,19 +1917,19 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">N</t>
+          <t xml:space="preserve">P</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">-10.5/10/E</t>
+          <t xml:space="preserve">-10/ZN</t>
         </is>
       </c>
       <c r="D21">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F21">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1547,19 +1940,209 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">K</t>
+          <t xml:space="preserve">P</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">-10.5/10/E</t>
+          <t xml:space="preserve">-10/ZN</t>
         </is>
       </c>
       <c r="D22">
         <v>35</v>
       </c>
       <c r="F22">
-        <v>2</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nr</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-10/ZN</t>
+        </is>
+      </c>
+      <c r="D23">
+        <v>41</v>
+      </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-10/ZN</t>
+        </is>
+      </c>
+      <c r="D24">
+        <v>21</v>
+      </c>
+      <c r="F24">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-10/ZN</t>
+        </is>
+      </c>
+      <c r="D25">
+        <v>20</v>
+      </c>
+      <c r="F25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-10/ZN</t>
+        </is>
+      </c>
+      <c r="D26">
+        <v>43</v>
+      </c>
+      <c r="F26">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-10/ZN</t>
+        </is>
+      </c>
+      <c r="D27">
+        <v>38</v>
+      </c>
+      <c r="F27">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-10/ZN</t>
+        </is>
+      </c>
+      <c r="D28">
+        <v>43</v>
+      </c>
+      <c r="F28">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-10/ZN</t>
+        </is>
+      </c>
+      <c r="D29">
+        <v>43</v>
+      </c>
+      <c r="F29">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-10/ZN</t>
+        </is>
+      </c>
+      <c r="D30" s="2">
+        <v>46</v>
+      </c>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2">
+        <v>2</v>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UWAGA: Wymiar 54 m łączy słup nr 7 (stacja 05-0497) ze słupem nr 3 (stacja 05-0498) - przęsło między stacjami, nie wliczono go do zestawienia.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1575,6 +2158,7 @@
     <col min="4" max="4" width="11" customWidth="1"/>
     <col min="5" max="5" width="8" customWidth="1"/>
     <col min="6" max="6" width="8" customWidth="1"/>
+    <col min="7" max="7" width="90" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1608,6 +2192,11 @@
           <t xml:space="preserve">Obwód</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kontrola</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1626,7 +2215,7 @@
         </is>
       </c>
       <c r="D2">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -1640,7 +2229,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">P</t>
+          <t xml:space="preserve">RPKr</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1649,7 +2238,7 @@
         </is>
       </c>
       <c r="D3">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -1672,7 +2261,7 @@
         </is>
       </c>
       <c r="D4">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="F4">
         <v>1</v>
@@ -1686,7 +2275,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">P</t>
+          <t xml:space="preserve">Nr</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1695,7 +2284,7 @@
         </is>
       </c>
       <c r="D5">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="F5">
         <v>1</v>
@@ -1709,7 +2298,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Or</t>
+          <t xml:space="preserve">Nr</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1718,7 +2307,7 @@
         </is>
       </c>
       <c r="D6">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -1727,7 +2316,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1741,16 +2330,16 @@
         </is>
       </c>
       <c r="D7">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="F7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1764,39 +2353,39 @@
         </is>
       </c>
       <c r="D8">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="F8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">P</t>
+          <t xml:space="preserve">K</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">-10/ZN</t>
+          <t xml:space="preserve">-10.5/10/E</t>
         </is>
       </c>
       <c r="D9">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="F9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1810,7 +2399,7 @@
         </is>
       </c>
       <c r="D10">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="F10">
         <v>2</v>
@@ -1819,12 +2408,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nr</t>
+          <t xml:space="preserve">P</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1833,7 +2422,7 @@
         </is>
       </c>
       <c r="D11">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="F11">
         <v>2</v>
@@ -1842,21 +2431,21 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">P</t>
+          <t xml:space="preserve">RPK</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">-10/ZN</t>
+          <t xml:space="preserve">-10.5/10/E</t>
         </is>
       </c>
       <c r="D12">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F12">
         <v>2</v>
@@ -1865,21 +2454,21 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nr</t>
+          <t xml:space="preserve">RPK</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">-10/ZN</t>
+          <t xml:space="preserve">-10.5/10/E</t>
         </is>
       </c>
       <c r="D13">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F13">
         <v>2</v>
@@ -1888,21 +2477,21 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">P</t>
+          <t xml:space="preserve">N</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">-10/ZN</t>
+          <t xml:space="preserve">-10.5/10/E</t>
         </is>
       </c>
       <c r="D14">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="F14">
         <v>2</v>
@@ -1911,23 +2500,184 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t xml:space="preserve">6</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RPK</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-10.5/10/E</t>
+        </is>
+      </c>
+      <c r="D15">
+        <v>53</v>
+      </c>
+      <c r="F15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6.1</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nr</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-10/ZN</t>
+        </is>
+      </c>
+      <c r="D16">
+        <v>8</v>
+      </c>
+      <c r="F16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6.2</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kr</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-10/ZN</t>
+        </is>
+      </c>
+      <c r="D17">
+        <v>53</v>
+      </c>
+      <c r="F17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-10/ZN</t>
+        </is>
+      </c>
+      <c r="D18">
+        <v>46</v>
+      </c>
+      <c r="F18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-10/ZN</t>
+        </is>
+      </c>
+      <c r="D19">
+        <v>44</v>
+      </c>
+      <c r="F19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t xml:space="preserve">9</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Kr</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-10/ZN</t>
-        </is>
-      </c>
-      <c r="D15">
-        <v>51</v>
-      </c>
-      <c r="F15">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-10/ZN</t>
+        </is>
+      </c>
+      <c r="D20">
+        <v>53</v>
+      </c>
+      <c r="F20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-10.5/10/E</t>
+        </is>
+      </c>
+      <c r="D21">
+        <v>42</v>
+      </c>
+      <c r="F21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">K</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-10.5/10/E</t>
+        </is>
+      </c>
+      <c r="D22">
+        <v>35</v>
+      </c>
+      <c r="F22">
         <v>2</v>
       </c>
     </row>
@@ -1944,6 +2694,7 @@
     <col min="4" max="4" width="11" customWidth="1"/>
     <col min="5" max="5" width="8" customWidth="1"/>
     <col min="6" max="6" width="8" customWidth="1"/>
+    <col min="7" max="7" width="90" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1977,6 +2728,11 @@
           <t xml:space="preserve">Obwód</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kontrola</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1986,16 +2742,16 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">N</t>
+          <t xml:space="preserve">P</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">-10.5/10/E</t>
+          <t xml:space="preserve">-10/ZN</t>
         </is>
       </c>
       <c r="D2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -2018,7 +2774,7 @@
         </is>
       </c>
       <c r="D3">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -2041,7 +2797,7 @@
         </is>
       </c>
       <c r="D4">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F4">
         <v>1</v>
@@ -2064,7 +2820,7 @@
         </is>
       </c>
       <c r="D5">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F5">
         <v>1</v>
@@ -2078,16 +2834,16 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">N</t>
+          <t xml:space="preserve">Or</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">-10.5/10/E</t>
+          <t xml:space="preserve">-10/ZN</t>
         </is>
       </c>
       <c r="D6">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -2096,7 +2852,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2110,53 +2866,53 @@
         </is>
       </c>
       <c r="D7">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="F7">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">K</t>
+          <t xml:space="preserve">P</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">-10.5/10/E</t>
+          <t xml:space="preserve">-10/ZN</t>
         </is>
       </c>
       <c r="D8">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="F8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">K</t>
+          <t xml:space="preserve">P</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">-10.5/10/E</t>
+          <t xml:space="preserve">-10/ZN</t>
         </is>
       </c>
       <c r="D9">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="F9">
         <v>2</v>
@@ -2165,7 +2921,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2179,7 +2935,7 @@
         </is>
       </c>
       <c r="D10">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F10">
         <v>2</v>
@@ -2188,12 +2944,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">P</t>
+          <t xml:space="preserve">Nr</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2202,7 +2958,7 @@
         </is>
       </c>
       <c r="D11">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F11">
         <v>2</v>
@@ -2211,7 +2967,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2225,7 +2981,7 @@
         </is>
       </c>
       <c r="D12">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F12">
         <v>2</v>
@@ -2234,12 +2990,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">P</t>
+          <t xml:space="preserve">Nr</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2248,7 +3004,7 @@
         </is>
       </c>
       <c r="D13">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F13">
         <v>2</v>
@@ -2257,7 +3013,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2271,9 +3027,32 @@
         </is>
       </c>
       <c r="D14">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kr</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-10/ZN</t>
+        </is>
+      </c>
+      <c r="D15">
+        <v>51</v>
+      </c>
+      <c r="F15">
         <v>2</v>
       </c>
     </row>
@@ -2290,6 +3069,7 @@
     <col min="4" max="4" width="11" customWidth="1"/>
     <col min="5" max="5" width="8" customWidth="1"/>
     <col min="6" max="6" width="8" customWidth="1"/>
+    <col min="7" max="7" width="90" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2323,6 +3103,11 @@
           <t xml:space="preserve">Obwód</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kontrola</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2332,16 +3117,16 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">P</t>
+          <t xml:space="preserve">N</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">-10/ZN</t>
+          <t xml:space="preserve">-10.5/10/E</t>
         </is>
       </c>
       <c r="D2">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -2355,7 +3140,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">RPKr</t>
+          <t xml:space="preserve">P</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -2364,7 +3149,7 @@
         </is>
       </c>
       <c r="D3">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -2373,7 +3158,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2387,7 +3172,7 @@
         </is>
       </c>
       <c r="D4">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="F4">
         <v>1</v>
@@ -2396,12 +3181,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nr</t>
+          <t xml:space="preserve">P</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2410,7 +3195,7 @@
         </is>
       </c>
       <c r="D5">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="F5">
         <v>1</v>
@@ -2419,21 +3204,21 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">P</t>
+          <t xml:space="preserve">N</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">-10/ZN</t>
+          <t xml:space="preserve">-10.5/10/E</t>
         </is>
       </c>
       <c r="D6">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -2442,7 +3227,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2456,7 +3241,7 @@
         </is>
       </c>
       <c r="D7">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="F7">
         <v>1</v>
@@ -2465,21 +3250,21 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.5</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kr</t>
+          <t xml:space="preserve">K</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">-10/ZN</t>
+          <t xml:space="preserve">-10.5/10/E</t>
         </is>
       </c>
       <c r="D8">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F8">
         <v>1</v>
@@ -2488,30 +3273,30 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">P</t>
+          <t xml:space="preserve">K</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">-10/ZN</t>
+          <t xml:space="preserve">-10.5/10/E</t>
         </is>
       </c>
       <c r="D9">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2525,16 +3310,16 @@
         </is>
       </c>
       <c r="D10">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="F10">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2548,16 +3333,16 @@
         </is>
       </c>
       <c r="D11">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="F11">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2571,16 +3356,16 @@
         </is>
       </c>
       <c r="D12">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F12">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2594,378 +3379,39 @@
         </is>
       </c>
       <c r="D13">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="F13">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-10/ZN</t>
-        </is>
-      </c>
-      <c r="D14">
-        <v>30</v>
-      </c>
-      <c r="F14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-10/ZN</t>
-        </is>
-      </c>
-      <c r="D15">
-        <v>36</v>
-      </c>
-      <c r="F15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-10/ZN</t>
-        </is>
-      </c>
-      <c r="D16">
-        <v>28</v>
-      </c>
-      <c r="F16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Kr</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-10/ZN</t>
-        </is>
-      </c>
-      <c r="D17">
-        <v>32</v>
-      </c>
-      <c r="F17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RPK</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-10.5/10/E</t>
-        </is>
-      </c>
-      <c r="D18">
-        <v>17</v>
-      </c>
-      <c r="F18">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1.1</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">K</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-10.5/10/E</t>
-        </is>
-      </c>
-      <c r="D19">
-        <v>48</v>
-      </c>
-      <c r="F19">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-10/ZN</t>
-        </is>
-      </c>
-      <c r="D20">
-        <v>17</v>
-      </c>
-      <c r="F20">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-10/ZN</t>
-        </is>
-      </c>
-      <c r="D21">
-        <v>53</v>
-      </c>
-      <c r="F21">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-10/ZN</t>
-        </is>
-      </c>
-      <c r="D22">
-        <v>21</v>
-      </c>
-      <c r="F22">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-10/ZN</t>
-        </is>
-      </c>
-      <c r="D23">
-        <v>24</v>
-      </c>
-      <c r="F23">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-10/ZN</t>
-        </is>
-      </c>
-      <c r="D24">
-        <v>53</v>
-      </c>
-      <c r="F24">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-10/ZN</t>
-        </is>
-      </c>
-      <c r="D25">
-        <v>53</v>
-      </c>
-      <c r="F25">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-10/ZN</t>
-        </is>
-      </c>
-      <c r="D26">
-        <v>49</v>
-      </c>
-      <c r="F26">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-10/ZN</t>
-        </is>
-      </c>
-      <c r="D27">
-        <v>43</v>
-      </c>
-      <c r="F27">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-10/ZN</t>
-        </is>
-      </c>
-      <c r="D28">
-        <v>47</v>
-      </c>
-      <c r="F28">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Nrp</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-10/ZN</t>
-        </is>
-      </c>
-      <c r="D29">
-        <v>46</v>
-      </c>
-      <c r="F29">
-        <v>2</v>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-10/ZN</t>
+        </is>
+      </c>
+      <c r="D14" s="2">
+        <v>42</v>
+      </c>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2">
+        <v>2</v>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UWAGA: Wymiar 31 m łączy słup nr 6 (stacja 05-0505) ze słupem nr 5 (stacja 05-0504) - przęsło między stacjami, nie wliczono go do zestawienia.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -2981,6 +3427,7 @@
     <col min="4" max="4" width="11" customWidth="1"/>
     <col min="5" max="5" width="8" customWidth="1"/>
     <col min="6" max="6" width="8" customWidth="1"/>
+    <col min="7" max="7" width="90" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3014,6 +3461,11 @@
           <t xml:space="preserve">Obwód</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kontrola</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3032,7 +3484,7 @@
         </is>
       </c>
       <c r="D2">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -3046,16 +3498,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">RPK</t>
+          <t xml:space="preserve">RPKr</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">-10.5/10/E</t>
+          <t xml:space="preserve">-10/ZN</t>
         </is>
       </c>
       <c r="D3">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -3069,16 +3521,16 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">N</t>
+          <t xml:space="preserve">P</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">-10.5/10/E</t>
+          <t xml:space="preserve">-10/ZN</t>
         </is>
       </c>
       <c r="D4">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="F4">
         <v>1</v>
@@ -3092,7 +3544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">P</t>
+          <t xml:space="preserve">Nr</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3101,7 +3553,7 @@
         </is>
       </c>
       <c r="D5">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="F5">
         <v>1</v>
@@ -3124,7 +3576,7 @@
         </is>
       </c>
       <c r="D6">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -3161,7 +3613,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">P</t>
+          <t xml:space="preserve">Kr</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3170,7 +3622,7 @@
         </is>
       </c>
       <c r="D8">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="F8">
         <v>1</v>
@@ -3179,21 +3631,21 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">N</t>
+          <t xml:space="preserve">P</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">-10.5/10/E</t>
+          <t xml:space="preserve">-10/ZN</t>
         </is>
       </c>
       <c r="D9">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="F9">
         <v>1</v>
@@ -3202,7 +3654,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.7</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -3216,7 +3668,7 @@
         </is>
       </c>
       <c r="D10">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="F10">
         <v>1</v>
@@ -3225,21 +3677,21 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.8</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">N</t>
+          <t xml:space="preserve">P</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-10.5/10/E</t>
+          <t xml:space="preserve">-10/ZN</t>
         </is>
       </c>
       <c r="D11">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="F11">
         <v>1</v>
@@ -3248,7 +3700,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.9</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3262,7 +3714,7 @@
         </is>
       </c>
       <c r="D12">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="F12">
         <v>1</v>
@@ -3271,21 +3723,21 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.10</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">N</t>
+          <t xml:space="preserve">P</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">-10.5/10/E</t>
+          <t xml:space="preserve">-10/ZN</t>
         </is>
       </c>
       <c r="D13">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F13">
         <v>1</v>
@@ -3294,21 +3746,21 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.11</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">N</t>
+          <t xml:space="preserve">P</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">-10.5/10/E</t>
+          <t xml:space="preserve">-10/ZN</t>
         </is>
       </c>
       <c r="D14">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="F14">
         <v>1</v>
@@ -3317,7 +3769,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.12</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3331,7 +3783,7 @@
         </is>
       </c>
       <c r="D15">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="F15">
         <v>1</v>
@@ -3340,7 +3792,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.13</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3354,7 +3806,7 @@
         </is>
       </c>
       <c r="D16">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="F16">
         <v>1</v>
@@ -3363,12 +3815,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.14</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">P</t>
+          <t xml:space="preserve">Kr</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -3377,62 +3829,68 @@
         </is>
       </c>
       <c r="D17">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="F17">
         <v>1</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2.15</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-10/ZN</t>
-        </is>
-      </c>
-      <c r="D18">
-        <v>46</v>
-      </c>
-      <c r="F18">
-        <v>1</v>
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RPK</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-10.5/10/E</t>
+        </is>
+      </c>
+      <c r="D18" s="2">
+        <v>17</v>
+      </c>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2">
+        <v>2</v>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UWAGA: Nie rozpoznano opisu "obw. nr" dla tego obwodu - przyjęto obwód 2.</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.16</t>
+          <t xml:space="preserve">1.1</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">P</t>
+          <t xml:space="preserve">K</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">-10/ZN</t>
+          <t xml:space="preserve">-10.5/10/E</t>
         </is>
       </c>
       <c r="D19">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F19">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.17</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -3446,21 +3904,21 @@
         </is>
       </c>
       <c r="D20">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="F20">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.18</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kr</t>
+          <t xml:space="preserve">P</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3469,16 +3927,16 @@
         </is>
       </c>
       <c r="D21">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="F21">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -3492,16 +3950,16 @@
         </is>
       </c>
       <c r="D22">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="F22">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3511,20 +3969,20 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">-10.5/10/E</t>
+          <t xml:space="preserve">-10/ZN</t>
         </is>
       </c>
       <c r="D23">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="F23">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3538,16 +3996,16 @@
         </is>
       </c>
       <c r="D24">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="F24">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3561,16 +4019,16 @@
         </is>
       </c>
       <c r="D25">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="F25">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3587,41 +4045,41 @@
         <v>49</v>
       </c>
       <c r="F26">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve">RPK</t>
+          <t xml:space="preserve">P</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">-10.5/10/E</t>
+          <t xml:space="preserve">-10/ZN</t>
         </is>
       </c>
       <c r="D27">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="F27">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nr</t>
+          <t xml:space="preserve">P</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3630,654 +4088,39 @@
         </is>
       </c>
       <c r="D28">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="F28">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RPKr</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-10/ZN</t>
-        </is>
-      </c>
-      <c r="D29">
-        <v>15</v>
-      </c>
-      <c r="F29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">11</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Nr</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-10/ZN</t>
-        </is>
-      </c>
-      <c r="D30">
-        <v>28</v>
-      </c>
-      <c r="F30">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-10/ZN</t>
-        </is>
-      </c>
-      <c r="D31">
-        <v>50</v>
-      </c>
-      <c r="F31">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-10/ZN</t>
-        </is>
-      </c>
-      <c r="D32">
-        <v>45</v>
-      </c>
-      <c r="F32">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Nr</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-10/ZN</t>
-        </is>
-      </c>
-      <c r="D33">
-        <v>36</v>
-      </c>
-      <c r="F33">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-10.5/10/E</t>
-        </is>
-      </c>
-      <c r="D34">
-        <v>14</v>
-      </c>
-      <c r="F34">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-10/ZN</t>
-        </is>
-      </c>
-      <c r="D35">
-        <v>34</v>
-      </c>
-      <c r="F35">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">K</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-10.5/10/E</t>
-        </is>
-      </c>
-      <c r="D36">
-        <v>27</v>
-      </c>
-      <c r="F36">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Nr</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-10/ZN</t>
-        </is>
-      </c>
-      <c r="D37">
-        <v>24</v>
-      </c>
-      <c r="F37">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1.1</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-10/ZN</t>
-        </is>
-      </c>
-      <c r="D38">
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nrp</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-10/ZN</t>
+        </is>
+      </c>
+      <c r="D29" s="2">
         <v>46</v>
       </c>
-      <c r="F38">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1.2</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Nr</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-10/ZN</t>
-        </is>
-      </c>
-      <c r="D39">
-        <v>51</v>
-      </c>
-      <c r="F39">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1.3</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-10/ZN</t>
-        </is>
-      </c>
-      <c r="D40">
-        <v>48</v>
-      </c>
-      <c r="F40">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1.4</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-10/ZN</t>
-        </is>
-      </c>
-      <c r="D41">
-        <v>51</v>
-      </c>
-      <c r="F41">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1.5</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Kr</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-10/ZN</t>
-        </is>
-      </c>
-      <c r="D42">
-        <v>50</v>
-      </c>
-      <c r="F42">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-10/ZN</t>
-        </is>
-      </c>
-      <c r="D43">
-        <v>24</v>
-      </c>
-      <c r="F43">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-10/ZN</t>
-        </is>
-      </c>
-      <c r="D44">
-        <v>45</v>
-      </c>
-      <c r="F44">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3.1</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Nr</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-10/ZN</t>
-        </is>
-      </c>
-      <c r="D45">
-        <v>8</v>
-      </c>
-      <c r="F45">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3.2</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-10/ZN</t>
-        </is>
-      </c>
-      <c r="D46">
-        <v>44</v>
-      </c>
-      <c r="F46">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3.3</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Nr</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-10/ZN</t>
-        </is>
-      </c>
-      <c r="D47">
-        <v>48</v>
-      </c>
-      <c r="F47">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3.4</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-10/ZN</t>
-        </is>
-      </c>
-      <c r="D48">
-        <v>35</v>
-      </c>
-      <c r="F48">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3.5</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Or</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-10/ZN</t>
-        </is>
-      </c>
-      <c r="D49">
-        <v>45</v>
-      </c>
-      <c r="F49">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3.6</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-10/ZN</t>
-        </is>
-      </c>
-      <c r="D50">
-        <v>38</v>
-      </c>
-      <c r="F50">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3.7</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-10/ZN</t>
-        </is>
-      </c>
-      <c r="D51">
-        <v>41</v>
-      </c>
-      <c r="F51">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3.8</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">K</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-10.5/10/E</t>
-        </is>
-      </c>
-      <c r="D52">
-        <v>41</v>
-      </c>
-      <c r="F52">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-10/ZN</t>
-        </is>
-      </c>
-      <c r="D53">
-        <v>51</v>
-      </c>
-      <c r="F53">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-10/ZN</t>
-        </is>
-      </c>
-      <c r="D54">
-        <v>43</v>
-      </c>
-      <c r="F54">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-10/ZN</t>
-        </is>
-      </c>
-      <c r="D55">
-        <v>49</v>
-      </c>
-      <c r="F55">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Kr</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-10/ZN</t>
-        </is>
-      </c>
-      <c r="D56">
-        <v>51</v>
-      </c>
-      <c r="F56">
-        <v>2</v>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2">
+        <v>2</v>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UWAGA: Wymiar 46 m łączy słup nr 11 (stacja 05-0506) ze słupem nr 10 (stacja 05-0982) - przęsło między stacjami, nie wliczono go do zestawienia.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -4293,6 +4136,7 @@
     <col min="4" max="4" width="11" customWidth="1"/>
     <col min="5" max="5" width="8" customWidth="1"/>
     <col min="6" max="6" width="8" customWidth="1"/>
+    <col min="7" max="7" width="90" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4326,6 +4170,11 @@
           <t xml:space="preserve">Obwód</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kontrola</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4344,7 +4193,7 @@
         </is>
       </c>
       <c r="D2">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -4358,48 +4207,54 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">P</t>
+          <t xml:space="preserve">RPK</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">-10/ZN</t>
+          <t xml:space="preserve">-10.5/10/E</t>
         </is>
       </c>
       <c r="D3">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F3">
         <v>1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-10/ZN</t>
-        </is>
-      </c>
-      <c r="D4">
-        <v>19</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.1</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-10.5/10/E</t>
+        </is>
+      </c>
+      <c r="D4" s="3">
+        <v>26</v>
+      </c>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3">
+        <v>1</v>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BŁĄD: Brak wymiaru do słupa nr 2 - odległość ustalona przez podział wymiaru 52 m ze słupem nr 2.2 (dorysuj wymiar).</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2.2</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -4422,7 +4277,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2.3</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -4436,7 +4291,7 @@
         </is>
       </c>
       <c r="D6">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -4445,7 +4300,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2.4</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -4459,7 +4314,7 @@
         </is>
       </c>
       <c r="D7">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="F7">
         <v>1</v>
@@ -4468,7 +4323,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">2.5</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -4482,7 +4337,7 @@
         </is>
       </c>
       <c r="D8">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="F8">
         <v>1</v>
@@ -4491,21 +4346,21 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.1</t>
+          <t xml:space="preserve">2.6</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">P</t>
+          <t xml:space="preserve">N</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">-10/ZN</t>
+          <t xml:space="preserve">-10.5/10/E</t>
         </is>
       </c>
       <c r="D9">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="F9">
         <v>1</v>
@@ -4514,7 +4369,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.2</t>
+          <t xml:space="preserve">2.7</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4528,7 +4383,7 @@
         </is>
       </c>
       <c r="D10">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="F10">
         <v>1</v>
@@ -4537,21 +4392,21 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.3</t>
+          <t xml:space="preserve">2.8</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kr</t>
+          <t xml:space="preserve">N</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-10/ZN</t>
+          <t xml:space="preserve">-10.5/10/E</t>
         </is>
       </c>
       <c r="D11">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="F11">
         <v>1</v>
@@ -4560,21 +4415,21 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.4</t>
+          <t xml:space="preserve">2.9</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">N</t>
+          <t xml:space="preserve">P</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">-10.5/10/E</t>
+          <t xml:space="preserve">-10/ZN</t>
         </is>
       </c>
       <c r="D12">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="F12">
         <v>1</v>
@@ -4583,21 +4438,21 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.5</t>
+          <t xml:space="preserve">2.10</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">P</t>
+          <t xml:space="preserve">N</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">-10/ZN</t>
+          <t xml:space="preserve">-10.5/10/E</t>
         </is>
       </c>
       <c r="D13">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F13">
         <v>1</v>
@@ -4606,12 +4461,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.6</t>
+          <t xml:space="preserve">2.11</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">K</t>
+          <t xml:space="preserve">N</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -4620,7 +4475,7 @@
         </is>
       </c>
       <c r="D14">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F14">
         <v>1</v>
@@ -4629,7 +4484,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">2.12</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4643,7 +4498,7 @@
         </is>
       </c>
       <c r="D15">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="F15">
         <v>1</v>
@@ -4652,7 +4507,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">2.13</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4675,12 +4530,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">2.14</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kr</t>
+          <t xml:space="preserve">P</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -4689,7 +4544,7 @@
         </is>
       </c>
       <c r="D17">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F17">
         <v>1</v>
@@ -4698,12 +4553,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2.15</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">RPKr</t>
+          <t xml:space="preserve">P</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -4712,16 +4567,16 @@
         </is>
       </c>
       <c r="D18">
-        <v>8</v>
+        <v>46</v>
       </c>
       <c r="F18">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.1</t>
+          <t xml:space="preserve">2.16</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4735,21 +4590,21 @@
         </is>
       </c>
       <c r="D19">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="F19">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.2</t>
+          <t xml:space="preserve">2.17</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">RPKr</t>
+          <t xml:space="preserve">P</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -4758,21 +4613,21 @@
         </is>
       </c>
       <c r="D20">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F20">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.3</t>
+          <t xml:space="preserve">2.18</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">P</t>
+          <t xml:space="preserve">Kr</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -4781,16 +4636,16 @@
         </is>
       </c>
       <c r="D21">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F21">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4804,44 +4659,44 @@
         </is>
       </c>
       <c r="D22">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="F22">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.5</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kr</t>
+          <t xml:space="preserve">P</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">-10/ZN</t>
+          <t xml:space="preserve">-10.5/10/E</t>
         </is>
       </c>
       <c r="D23">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="F23">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.6</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Or</t>
+          <t xml:space="preserve">P</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -4850,21 +4705,21 @@
         </is>
       </c>
       <c r="D24">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F24">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.7</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nr</t>
+          <t xml:space="preserve">P</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -4873,44 +4728,44 @@
         </is>
       </c>
       <c r="D25">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="F25">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.8</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">N</t>
+          <t xml:space="preserve">P</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">-10.5/10/E</t>
+          <t xml:space="preserve">-10/ZN</t>
         </is>
       </c>
       <c r="D26">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="F26">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.9</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve">K</t>
+          <t xml:space="preserve">RPK</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4919,21 +4774,21 @@
         </is>
       </c>
       <c r="D27">
-        <v>61</v>
+        <v>23</v>
       </c>
       <c r="F27">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">P</t>
+          <t xml:space="preserve">Nr</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4942,21 +4797,21 @@
         </is>
       </c>
       <c r="D28">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F28">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">P</t>
+          <t xml:space="preserve">RPKr</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4965,21 +4820,21 @@
         </is>
       </c>
       <c r="D29">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="F29">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">P</t>
+          <t xml:space="preserve">Nr</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4988,16 +4843,16 @@
         </is>
       </c>
       <c r="D30">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F30">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -5011,21 +4866,21 @@
         </is>
       </c>
       <c r="D31">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="F31">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Or</t>
+          <t xml:space="preserve">P</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -5034,21 +4889,21 @@
         </is>
       </c>
       <c r="D32">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="F32">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t xml:space="preserve">P</t>
+          <t xml:space="preserve">Nr</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -5057,39 +4912,39 @@
         </is>
       </c>
       <c r="D33">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="F33">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t xml:space="preserve">P</t>
+          <t xml:space="preserve">N</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve">-10/ZN</t>
+          <t xml:space="preserve">-10.5/10/E</t>
         </is>
       </c>
       <c r="D34">
-        <v>52</v>
+        <v>14</v>
       </c>
       <c r="F34">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -5103,44 +4958,44 @@
         </is>
       </c>
       <c r="D35">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="F35">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t xml:space="preserve">P</t>
+          <t xml:space="preserve">K</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve">-10/ZN</t>
+          <t xml:space="preserve">-10.5/10/E</t>
         </is>
       </c>
       <c r="D36">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="F36">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t xml:space="preserve">P</t>
+          <t xml:space="preserve">Nr</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5149,7 +5004,7 @@
         </is>
       </c>
       <c r="D37">
-        <v>54</v>
+        <v>24</v>
       </c>
       <c r="F37">
         <v>2</v>
@@ -5158,12 +5013,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1.1</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nr</t>
+          <t xml:space="preserve">P</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5172,7 +5027,7 @@
         </is>
       </c>
       <c r="D38">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F38">
         <v>2</v>
@@ -5181,21 +5036,21 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">1.2</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t xml:space="preserve">N</t>
+          <t xml:space="preserve">Nr</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t xml:space="preserve">-10.5/10/E</t>
+          <t xml:space="preserve">-10/ZN</t>
         </is>
       </c>
       <c r="D39">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="F39">
         <v>2</v>
@@ -5204,7 +5059,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">1.3</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -5218,7 +5073,7 @@
         </is>
       </c>
       <c r="D40">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="F40">
         <v>2</v>
@@ -5227,7 +5082,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">1.4</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5241,7 +5096,7 @@
         </is>
       </c>
       <c r="D41">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F41">
         <v>2</v>
@@ -5250,12 +5105,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">1.5</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t xml:space="preserve">P</t>
+          <t xml:space="preserve">Kr</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -5264,7 +5119,7 @@
         </is>
       </c>
       <c r="D42">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="F42">
         <v>2</v>
@@ -5273,23 +5128,322 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
+          <t xml:space="preserve">P</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-10/ZN</t>
+        </is>
+      </c>
+      <c r="D43">
+        <v>24</v>
+      </c>
+      <c r="F43">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-10/ZN</t>
+        </is>
+      </c>
+      <c r="D44">
+        <v>45</v>
+      </c>
+      <c r="F44">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.1</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-10/ZN</t>
+        </is>
+      </c>
+      <c r="D45">
+        <v>8</v>
+      </c>
+      <c r="F45">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.2</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-10/ZN</t>
+        </is>
+      </c>
+      <c r="D46">
+        <v>44</v>
+      </c>
+      <c r="F46">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.3</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nr</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-10/ZN</t>
+        </is>
+      </c>
+      <c r="D47">
+        <v>48</v>
+      </c>
+      <c r="F47">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.4</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-10/ZN</t>
+        </is>
+      </c>
+      <c r="D48">
+        <v>35</v>
+      </c>
+      <c r="F48">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.5</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Or</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-10/ZN</t>
+        </is>
+      </c>
+      <c r="D49">
+        <v>45</v>
+      </c>
+      <c r="F49">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.6</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-10/ZN</t>
+        </is>
+      </c>
+      <c r="D50">
+        <v>38</v>
+      </c>
+      <c r="F50">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.7</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-10/ZN</t>
+        </is>
+      </c>
+      <c r="D51">
+        <v>41</v>
+      </c>
+      <c r="F51">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.8</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
           <t xml:space="preserve">K</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t xml:space="preserve">-10.5/10/E</t>
         </is>
       </c>
-      <c r="D43">
-        <v>54</v>
-      </c>
-      <c r="F43">
+      <c r="D52">
+        <v>41</v>
+      </c>
+      <c r="F52">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-10/ZN</t>
+        </is>
+      </c>
+      <c r="D53">
+        <v>51</v>
+      </c>
+      <c r="F53">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-10/ZN</t>
+        </is>
+      </c>
+      <c r="D54">
+        <v>43</v>
+      </c>
+      <c r="F54">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-10/ZN</t>
+        </is>
+      </c>
+      <c r="D55">
+        <v>49</v>
+      </c>
+      <c r="F55">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kr</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-10/ZN</t>
+        </is>
+      </c>
+      <c r="D56">
+        <v>51</v>
+      </c>
+      <c r="F56">
         <v>2</v>
       </c>
     </row>
@@ -5306,6 +5460,7 @@
     <col min="4" max="4" width="11" customWidth="1"/>
     <col min="5" max="5" width="8" customWidth="1"/>
     <col min="6" max="6" width="8" customWidth="1"/>
+    <col min="7" max="7" width="90" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5339,6 +5494,11 @@
           <t xml:space="preserve">Obwód</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kontrola</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5357,7 +5517,7 @@
         </is>
       </c>
       <c r="D2">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -5380,7 +5540,7 @@
         </is>
       </c>
       <c r="D3">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -5403,7 +5563,7 @@
         </is>
       </c>
       <c r="D4">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="F4">
         <v>1</v>
@@ -5426,7 +5586,7 @@
         </is>
       </c>
       <c r="D5">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="F5">
         <v>1</v>
@@ -5440,7 +5600,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">RPKr</t>
+          <t xml:space="preserve">P</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -5449,7 +5609,7 @@
         </is>
       </c>
       <c r="D6">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -5472,7 +5632,7 @@
         </is>
       </c>
       <c r="D7">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="F7">
         <v>1</v>
@@ -5486,7 +5646,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nr</t>
+          <t xml:space="preserve">P</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -5495,7 +5655,7 @@
         </is>
       </c>
       <c r="D8">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="F8">
         <v>1</v>
@@ -5504,7 +5664,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">7.1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -5518,7 +5678,7 @@
         </is>
       </c>
       <c r="D9">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="F9">
         <v>1</v>
@@ -5527,21 +5687,21 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">7.2</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">N</t>
+          <t xml:space="preserve">P</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">-10.5/10/E</t>
+          <t xml:space="preserve">-10/ZN</t>
         </is>
       </c>
       <c r="D10">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="F10">
         <v>1</v>
@@ -5550,12 +5710,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">7.3</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">P</t>
+          <t xml:space="preserve">Kr</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -5564,7 +5724,7 @@
         </is>
       </c>
       <c r="D11">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="F11">
         <v>1</v>
@@ -5573,32 +5733,35 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7.4</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Or</t>
+          <t xml:space="preserve">N</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">-10/ZN</t>
-        </is>
+          <t xml:space="preserve">-10.5/10/E</t>
+        </is>
+      </c>
+      <c r="D12">
+        <v>14</v>
       </c>
       <c r="F12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">7.5</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">RPKr</t>
+          <t xml:space="preserve">P</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -5607,44 +5770,44 @@
         </is>
       </c>
       <c r="D13">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="F13">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.1</t>
+          <t xml:space="preserve">7.6</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">P</t>
+          <t xml:space="preserve">K</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">-10/ZN</t>
+          <t xml:space="preserve">-10.5/10/E</t>
         </is>
       </c>
       <c r="D14">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="F14">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kr</t>
+          <t xml:space="preserve">P</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -5653,16 +5816,16 @@
         </is>
       </c>
       <c r="D15">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="F15">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -5676,21 +5839,21 @@
         </is>
       </c>
       <c r="D16">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="F16">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">P</t>
+          <t xml:space="preserve">Kr</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -5699,21 +5862,21 @@
         </is>
       </c>
       <c r="D17">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F17">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">P</t>
+          <t xml:space="preserve">RPKr</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -5722,7 +5885,7 @@
         </is>
       </c>
       <c r="D18">
-        <v>46</v>
+        <v>8</v>
       </c>
       <c r="F18">
         <v>2</v>
@@ -5731,7 +5894,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1.1</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5745,7 +5908,7 @@
         </is>
       </c>
       <c r="D19">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="F19">
         <v>2</v>
@@ -5754,12 +5917,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1.2</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">P</t>
+          <t xml:space="preserve">RPKr</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -5768,7 +5931,7 @@
         </is>
       </c>
       <c r="D20">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="F20">
         <v>2</v>
@@ -5777,23 +5940,529 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t xml:space="preserve">1.3</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-10/ZN</t>
+        </is>
+      </c>
+      <c r="D21">
+        <v>35</v>
+      </c>
+      <c r="F21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.4</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-10/ZN</t>
+        </is>
+      </c>
+      <c r="D22">
+        <v>47</v>
+      </c>
+      <c r="F22">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.5</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kr</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-10/ZN</t>
+        </is>
+      </c>
+      <c r="D23">
+        <v>39</v>
+      </c>
+      <c r="F23">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.6</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Or</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-10/ZN</t>
+        </is>
+      </c>
+      <c r="D24">
+        <v>28</v>
+      </c>
+      <c r="F24">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.7</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nr</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-10/ZN</t>
+        </is>
+      </c>
+      <c r="D25">
+        <v>40</v>
+      </c>
+      <c r="F25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.8</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-10.5/10/E</t>
+        </is>
+      </c>
+      <c r="D26">
+        <v>27</v>
+      </c>
+      <c r="F26">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.9</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">K</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-10.5/10/E</t>
+        </is>
+      </c>
+      <c r="D27">
+        <v>61</v>
+      </c>
+      <c r="F27">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-10/ZN</t>
+        </is>
+      </c>
+      <c r="D28">
+        <v>35</v>
+      </c>
+      <c r="F28">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-10/ZN</t>
+        </is>
+      </c>
+      <c r="D29">
+        <v>27</v>
+      </c>
+      <c r="F29">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-10/ZN</t>
+        </is>
+      </c>
+      <c r="D30">
+        <v>29</v>
+      </c>
+      <c r="F30">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-10/ZN</t>
+        </is>
+      </c>
+      <c r="D31">
+        <v>26</v>
+      </c>
+      <c r="F31">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Or</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-10/ZN</t>
+        </is>
+      </c>
+      <c r="D32">
+        <v>39</v>
+      </c>
+      <c r="F32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-10/ZN</t>
+        </is>
+      </c>
+      <c r="D33">
+        <v>53</v>
+      </c>
+      <c r="F33">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t xml:space="preserve">8</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">P</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-10/ZN</t>
-        </is>
-      </c>
-      <c r="D21">
-        <v>46</v>
-      </c>
-      <c r="F21">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-10/ZN</t>
+        </is>
+      </c>
+      <c r="D34">
+        <v>52</v>
+      </c>
+      <c r="F34">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-10/ZN</t>
+        </is>
+      </c>
+      <c r="D35">
+        <v>51</v>
+      </c>
+      <c r="F35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-10/ZN</t>
+        </is>
+      </c>
+      <c r="D36">
+        <v>52</v>
+      </c>
+      <c r="F36">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-10/ZN</t>
+        </is>
+      </c>
+      <c r="D37">
+        <v>54</v>
+      </c>
+      <c r="F37">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nr</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-10/ZN</t>
+        </is>
+      </c>
+      <c r="D38">
+        <v>52</v>
+      </c>
+      <c r="F38">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-10.5/10/E</t>
+        </is>
+      </c>
+      <c r="D39">
+        <v>14</v>
+      </c>
+      <c r="F39">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-10/ZN</t>
+        </is>
+      </c>
+      <c r="D40">
+        <v>58</v>
+      </c>
+      <c r="F40">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-10/ZN</t>
+        </is>
+      </c>
+      <c r="D41">
+        <v>53</v>
+      </c>
+      <c r="F41">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-10/ZN</t>
+        </is>
+      </c>
+      <c r="D42">
+        <v>32</v>
+      </c>
+      <c r="F42">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">K</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-10.5/10/E</t>
+        </is>
+      </c>
+      <c r="D43">
+        <v>54</v>
+      </c>
+      <c r="F43">
         <v>2</v>
       </c>
     </row>
